--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0003T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.05601241351825</v>
+        <v>8.134102017196717</v>
       </c>
       <c r="D2" t="n">
-        <v>41.78862360140616</v>
+        <v>6.790651335228501</v>
       </c>
       <c r="E2" t="n">
-        <v>11.6032831929338</v>
+        <v>1.885533518851743</v>
       </c>
       <c r="F2" t="n">
-        <v>8.416999759174917</v>
+        <v>1.367762460865924</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.6296031581734</v>
+        <v>7.577310513203177</v>
       </c>
       <c r="D3" t="n">
-        <v>41.63954325517992</v>
+        <v>6.766425778966738</v>
       </c>
       <c r="E3" t="n">
-        <v>11.6032831929338</v>
+        <v>1.885533518851743</v>
       </c>
       <c r="F3" t="n">
-        <v>8.416999759174917</v>
+        <v>1.367762460865924</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>72.77756998154881</v>
+        <v>11.82635512200168</v>
       </c>
       <c r="D4" t="n">
-        <v>59.56876946710522</v>
+        <v>9.679925038404599</v>
       </c>
       <c r="E4" t="n">
-        <v>11.6032831929338</v>
+        <v>1.885533518851743</v>
       </c>
       <c r="F4" t="n">
-        <v>8.416999759174917</v>
+        <v>1.367762460865924</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
